--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -3839,7 +3839,7 @@
         <v>118567069</v>
       </c>
       <c r="B29" t="n">
-        <v>91124</v>
+        <v>91131</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4316,10 +4316,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121756567</v>
+        <v>121756572</v>
       </c>
       <c r="B33" t="n">
-        <v>90329</v>
+        <v>102425</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4328,30 +4328,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3086</v>
+        <v>223246</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4406,21 +4407,6 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4437,10 +4423,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121756572</v>
+        <v>121756567</v>
       </c>
       <c r="B34" t="n">
-        <v>102425</v>
+        <v>90329</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4449,31 +4435,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223246</v>
+        <v>3086</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4528,6 +4513,21 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4195,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121756575</v>
+        <v>121756572</v>
       </c>
       <c r="B32" t="n">
-        <v>88030</v>
+        <v>102425</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4207,30 +4207,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>861</v>
+        <v>223246</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Granulobasidium vellereum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ellis &amp; Cragin) Jülich</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4285,21 +4286,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4316,10 +4302,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121756572</v>
+        <v>121756567</v>
       </c>
       <c r="B33" t="n">
-        <v>102425</v>
+        <v>90329</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4328,31 +4314,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223246</v>
+        <v>3086</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4407,6 +4392,21 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4423,10 +4423,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121756567</v>
+        <v>121756575</v>
       </c>
       <c r="B34" t="n">
-        <v>90329</v>
+        <v>88030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4439,21 +4439,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3086</v>
+        <v>861</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Granulobasidium vellereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Ellis &amp; Cragin) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4195,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121756572</v>
+        <v>121756575</v>
       </c>
       <c r="B32" t="n">
-        <v>102425</v>
+        <v>88030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4207,31 +4207,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223246</v>
+        <v>861</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Granulobasidium vellereum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Ellis &amp; Cragin) Jülich</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4286,6 +4285,21 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4423,10 +4437,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121756575</v>
+        <v>121756572</v>
       </c>
       <c r="B34" t="n">
-        <v>88030</v>
+        <v>102425</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4435,30 +4449,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>861</v>
+        <v>223246</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Granulobasidium vellereum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ellis &amp; Cragin) Jülich</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4513,21 +4528,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4195,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121756575</v>
+        <v>121756567</v>
       </c>
       <c r="B32" t="n">
-        <v>88030</v>
+        <v>90329</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4211,21 +4211,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>861</v>
+        <v>3086</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Granulobasidium vellereum</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ellis &amp; Cragin) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121756567</v>
+        <v>121756572</v>
       </c>
       <c r="B33" t="n">
-        <v>90329</v>
+        <v>102425</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4328,30 +4328,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3086</v>
+        <v>223246</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4406,21 +4407,6 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4437,10 +4423,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121756572</v>
+        <v>121756575</v>
       </c>
       <c r="B34" t="n">
-        <v>102425</v>
+        <v>88030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4449,31 +4435,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223246</v>
+        <v>861</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Granulobasidium vellereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Ellis &amp; Cragin) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4528,6 +4513,21 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4195,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121756567</v>
+        <v>121756575</v>
       </c>
       <c r="B32" t="n">
-        <v>90329</v>
+        <v>88030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4211,21 +4211,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3086</v>
+        <v>861</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Granulobasidium vellereum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>(Ellis &amp; Cragin) Jülich</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121756572</v>
+        <v>121756567</v>
       </c>
       <c r="B33" t="n">
-        <v>102425</v>
+        <v>90329</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4328,31 +4328,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223246</v>
+        <v>3086</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4407,6 +4406,21 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4423,10 +4437,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121756575</v>
+        <v>121756572</v>
       </c>
       <c r="B34" t="n">
-        <v>88030</v>
+        <v>102425</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4435,30 +4449,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>861</v>
+        <v>223246</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Granulobasidium vellereum</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ellis &amp; Cragin) Jülich</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4513,21 +4528,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4195,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121756575</v>
+        <v>121756567</v>
       </c>
       <c r="B32" t="n">
-        <v>88030</v>
+        <v>90343</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4211,21 +4211,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>861</v>
+        <v>3086</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Granulobasidium vellereum</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ellis &amp; Cragin) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121756572</v>
+        <v>121756575</v>
       </c>
       <c r="B33" t="n">
-        <v>102425</v>
+        <v>88044</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4328,31 +4328,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223246</v>
+        <v>861</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Granulobasidium vellereum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Ellis &amp; Cragin) Jülich</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4407,6 +4406,21 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4423,10 +4437,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121756567</v>
+        <v>121756572</v>
       </c>
       <c r="B34" t="n">
-        <v>90329</v>
+        <v>102443</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4435,30 +4449,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3086</v>
+        <v>223246</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4513,21 +4528,6 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>121756567</v>
       </c>
       <c r="B32" t="n">
-        <v>90343</v>
+        <v>90345</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>121756575</v>
       </c>
       <c r="B33" t="n">
-        <v>88044</v>
+        <v>88046</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>121756572</v>
       </c>
       <c r="B34" t="n">
-        <v>102443</v>
+        <v>102445</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>121756567</v>
       </c>
       <c r="B32" t="n">
-        <v>90345</v>
+        <v>90346</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>121756575</v>
       </c>
       <c r="B33" t="n">
-        <v>88046</v>
+        <v>88047</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>121756572</v>
       </c>
       <c r="B34" t="n">
-        <v>102445</v>
+        <v>102452</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4195,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121756567</v>
+        <v>121756572</v>
       </c>
       <c r="B32" t="n">
-        <v>90346</v>
+        <v>102461</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4207,30 +4207,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3086</v>
+        <v>223246</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartöra</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Auricularia mesenterica</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Dicks.:Fr.) Pers.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4285,21 +4286,6 @@
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>skogsalm</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Ulmus glabra</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4316,10 +4302,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121756575</v>
+        <v>121756567</v>
       </c>
       <c r="B33" t="n">
-        <v>88047</v>
+        <v>90355</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4332,21 +4318,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>861</v>
+        <v>3086</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almkrämskinn</t>
+          <t>Svartöra</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Granulobasidium vellereum</t>
+          <t>Auricularia mesenterica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ellis &amp; Cragin) Jülich</t>
+          <t>(Dicks.:Fr.) Pers.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4437,10 +4423,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121756572</v>
+        <v>121756575</v>
       </c>
       <c r="B34" t="n">
-        <v>102452</v>
+        <v>88056</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4449,31 +4435,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223246</v>
+        <v>861</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Almkrämskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Granulobasidium vellereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(Ellis &amp; Cragin) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4528,6 +4513,21 @@
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>skogsalm</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4542,6 +4542,225 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>124053196</v>
+      </c>
+      <c r="B35" t="n">
+        <v>95433</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Turelund, Kungshamn-Morga NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>648540</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6626487</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Niklas Hjort</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Niklas Lönnell, Åke Berg, Håkan Lernefalk, Mia Agvald Jägborn, Malin Lundberg, Anna Nyberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>124025705</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58033</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Turelund Vut 3, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>648530</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6626473</v>
+      </c>
+      <c r="S36" t="n">
+        <v>100</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4544,10 +4544,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124053196</v>
+        <v>124025705</v>
       </c>
       <c r="B35" t="n">
-        <v>95455</v>
+        <v>58055</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4560,41 +4560,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2818</v>
+        <v>102990</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Turelund, Kungshamn-Morga NR, Upl</t>
+          <t>Turelund Vut 3, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>648540</v>
+        <v>648530</v>
       </c>
       <c r="R35" t="n">
-        <v>6626487</v>
+        <v>6626473</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4621,54 +4617,43 @@
           <t>2025-04-13</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-13</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Niklas Hjort</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Niklas Lönnell, Åke Berg, Håkan Lernefalk, Mia Agvald Jägborn, Malin Lundberg, Anna Nyberg</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124025705</v>
+        <v>124053196</v>
       </c>
       <c r="B36" t="n">
-        <v>58055</v>
+        <v>95455</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4677,37 +4662,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102990</v>
+        <v>2818</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Turelund Vut 3, Upl</t>
+          <t>Turelund, Kungshamn-Morga NR, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>648530</v>
+        <v>648540</v>
       </c>
       <c r="R36" t="n">
-        <v>6626473</v>
+        <v>6626487</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4734,29 +4723,40 @@
           <t>2025-04-13</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-13</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Niklas Hjort</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Niklas Hjort, Tomas Hallingbäck, Karin Wiklund, Niklas Lönnell, Åke Berg, Håkan Lernefalk, Mia Agvald Jägborn, Malin Lundberg, Anna Nyberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4761,122 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>124904027</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58055</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kungshamn-Morga, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>648597</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6626395</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Knivsta</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Alsike</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>David van der Spoel</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4649,7 +4649,7 @@
         <v>124053196</v>
       </c>
       <c r="B36" t="n">
-        <v>95455</v>
+        <v>95623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>124904027</v>
       </c>
       <c r="B37" t="n">
-        <v>58055</v>
+        <v>58167</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 22387-2020 artfynd.xlsx
+++ b/artfynd/A 22387-2020 artfynd.xlsx
@@ -4768,11 +4768,6 @@
       <c r="B37" t="n">
         <v>58167</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>LC</t>
